--- a/EKG_Kalite_Yönetim_Sistemi/04_Parça ve Proses Kontrolü/01_PPC1 - Kontrol Planı, Muayene ve Serbest Bırakma/EKG-KLT-FRM-21_proses_kontrol_kayit_sablonu_parca_karakteristik_cihaz.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/04_Parça ve Proses Kontrolü/01_PPC1 - Kontrol Planı, Muayene ve Serbest Bırakma/EKG-KLT-FRM-21_proses_kontrol_kayit_sablonu_parca_karakteristik_cihaz.xlsx
@@ -966,7 +966,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-FRM-21&amp;C&amp;"Arial,Regular"&amp;11Proses Kontrol Kayıt Şablonu (parça, karakteristik, cihaz, sıklık ve sonuç)</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 10.06.2026 | Revizyon: 18.09.2026
+Revizyon nedeni: Kontrol planı ve gerçek numune izlenebilirliği korundu; tamlık hesabında geçersiz adetler görünür kılındı.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcfe950ba8aba4735"/>
   <x:tableParts count="1">
@@ -1410,7 +1411,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-FRM-21&amp;C&amp;"Arial,Regular"&amp;11Proses Kontrol Kayıt Şablonu (parça, karakteristik, cihaz, sıklık ve sonuç)</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 10.06.2026 | Revizyon: 18.09.2026
+Revizyon nedeni: Kontrol planı ve gerçek numune izlenebilirliği korundu; tamlık hesabında geçersiz adetler görünür kılındı.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1796284cdb8249f3"/>
   <x:tableParts count="1">
@@ -1753,7 +1755,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-FRM-21&amp;C&amp;"Arial,Regular"&amp;11Proses Kontrol Kayıt Şablonu (parça, karakteristik, cihaz, sıklık ve sonuç)</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 10.06.2026 | Revizyon: 18.09.2026
+Revizyon nedeni: Kontrol planı ve gerçek numune izlenebilirliği korundu; tamlık hesabında geçersiz adetler görünür kılındı.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raa17f071fde342da"/>
   <x:tableParts count="1">
